--- a/results/Int Task Remove ACC -0.2/Rando_2_permute.xlsx
+++ b/results/Int Task Remove ACC -0.2/Rando_2_permute.xlsx
@@ -440,817 +440,817 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6615383077504053</v>
+        <v>0.6577528489237399</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6685889774973899</v>
+        <v>0.6547020014661128</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6688939733878313</v>
+        <v>0.6667467845480597</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.674939023035742</v>
+        <v>0.6660801474998335</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6768143145922652</v>
+        <v>0.6720467823266766</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6751420574449652</v>
+        <v>0.6740344758646734</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6839669458204678</v>
+        <v>0.6791078925739165</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6870744385454384</v>
+        <v>0.6807801497212165</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6634118222005021</v>
+        <v>0.6794242175178267</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6298700490925651</v>
+        <v>0.6771079814292378</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6302316902503499</v>
+        <v>0.6824872825821356</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6319152764511184</v>
+        <v>0.7234275940200369</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6158489015260902</v>
+        <v>0.7220943199235844</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6156232090099296</v>
+        <v>0.7227269698114046</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6149452429082347</v>
+        <v>0.7227269698114046</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6069229402225826</v>
+        <v>0.7135753159917364</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6229779860941422</v>
+        <v>0.7210660417175734</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6798051847079992</v>
+        <v>0.7108974387453628</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6805397960770376</v>
+        <v>0.7051913721482995</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6586976031277073</v>
+        <v>0.7107501610502699</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6243034853499789</v>
+        <v>0.7099928915742941</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5904636026390031</v>
+        <v>0.7218328631405914</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5883277428527001</v>
+        <v>0.7218328631405914</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.587400537574694</v>
+        <v>0.7087371437456961</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.618109603038852</v>
+        <v>0.7313357176177888</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6219848057400538</v>
+        <v>0.710873003531999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6223124597374325</v>
+        <v>0.710873003531999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6223124597374325</v>
+        <v>0.6957764844392118</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6366952484616922</v>
+        <v>0.6996856743008197</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.631486771664038</v>
+        <v>0.6977424084234845</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6168094275495923</v>
+        <v>0.6943647955216918</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6159057689317369</v>
+        <v>0.6867938778683609</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6119512628562542</v>
+        <v>0.6572370437834596</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6116575960192816</v>
+        <v>0.6391489881600284</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6109116555967746</v>
+        <v>0.6408099162538596</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6109229846502433</v>
+        <v>0.6353191016727013</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6090128173801008</v>
+        <v>0.6502727858364619</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6067305684519182</v>
+        <v>0.606035053424262</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6060186151898171</v>
+        <v>0.6147144412110981</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6060072861363485</v>
+        <v>0.623810338316636</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5956905169158317</v>
+        <v>0.6308043627962769</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5910127285247795</v>
+        <v>0.629991336606171</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5766961370149055</v>
+        <v>0.6109507519381567</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5716558189128551</v>
+        <v>0.6102954439433992</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5928313748139592</v>
+        <v>0.6203743030410733</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6006733011973254</v>
+        <v>0.6301821534087122</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5860063975831353</v>
+        <v>0.6539771641824199</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5856787435857566</v>
+        <v>0.6605651198436147</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5882668769575938</v>
+        <v>0.6459548614967678</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6117699980007553</v>
+        <v>0.6879747650887442</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6130466268298642</v>
+        <v>0.6930255236910501</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6130466268298642</v>
+        <v>0.6930255236910501</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5875489259613035</v>
+        <v>0.6797589799409112</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5841259968456362</v>
+        <v>0.689646133682831</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.548195570562232</v>
+        <v>0.6936468445254016</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5490879001266188</v>
+        <v>0.6769147211053602</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5490879001266188</v>
+        <v>0.6724521847302131</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5429522180509585</v>
+        <v>0.6823628851322834</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5429522180509585</v>
+        <v>0.7061230201923718</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.544003154363907</v>
+        <v>0.6972641446564631</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5440606881844636</v>
+        <v>0.6580729502188062</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5348541662038785</v>
+        <v>0.6581635826465557</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5419379345580558</v>
+        <v>0.653045738276651</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5509545282893129</v>
+        <v>0.653045738276651</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5509545282893129</v>
+        <v>0.6608981051602728</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5511122464846613</v>
+        <v>0.6608981051602728</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5536201879290046</v>
+        <v>0.5903591976364485</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5567267921007619</v>
+        <v>0.5903591976364485</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5560714841060044</v>
+        <v>0.5902128084945687</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5711331274851723</v>
+        <v>0.5929020147944111</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5583084168203123</v>
+        <v>0.5936366261634494</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5211266854743763</v>
+        <v>0.5949472421529645</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5251604949241397</v>
+        <v>0.6068682941999689</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5249792300686408</v>
+        <v>0.5731661372370438</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5187764622253815</v>
+        <v>0.5763058400159939</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5253748583868316</v>
+        <v>0.574397449852278</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5042481729124553</v>
+        <v>0.574397449852278</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5012879578825777</v>
+        <v>0.5759790745718284</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4999320256791878</v>
+        <v>0.5756287624675123</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5009376457782616</v>
+        <v>0.5829495523913188</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5009376457782616</v>
+        <v>0.5986211875513695</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5009376457782616</v>
+        <v>0.5386169669236066</v>
       </c>
     </row>
     <row r="84">
@@ -1260,67 +1260,67 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5022482617677766</v>
+        <v>0.5386169669236066</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5005760046204767</v>
+        <v>0.5442428415931759</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4999773418930626</v>
+        <v>0.5428302641224426</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4996383588422152</v>
+        <v>0.5333405158051403</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5003276539973788</v>
+        <v>0.5270688850878557</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4999886709465313</v>
+        <v>0.51746406912944</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5003276539973788</v>
+        <v>0.501867294577604</v>
       </c>
     </row>
   </sheetData>
